--- a/artfynd/A 40331-2023 artfynd.xlsx
+++ b/artfynd/A 40331-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113028789</v>
+        <v>113029119</v>
       </c>
       <c r="B2" t="n">
-        <v>99554</v>
+        <v>90045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sofielund (Sofielund), Vstm</t>
+          <t>Ekbacken (Ekbacken), Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550387</v>
+        <v>550516</v>
       </c>
       <c r="R2" t="n">
-        <v>6583996</v>
+        <v>6584021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113029119</v>
+        <v>113028789</v>
       </c>
       <c r="B3" t="n">
-        <v>90029</v>
+        <v>99570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,39 +790,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ekbacken (Ekbacken), Vstm</t>
+          <t>Sofielund (Sofielund), Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550516</v>
+        <v>550387</v>
       </c>
       <c r="R3" t="n">
-        <v>6584021</v>
+        <v>6583996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40331-2023 artfynd.xlsx
+++ b/artfynd/A 40331-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
